--- a/Competencias/Competencias-modelo.xlsx
+++ b/Competencias/Competencias-modelo.xlsx
@@ -1726,11 +1726,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="38867580"/>
-        <c:axId val="78246966"/>
+        <c:axId val="588413"/>
+        <c:axId val="8915658"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="38867580"/>
+        <c:axId val="588413"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1762,7 +1762,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78246966"/>
+        <c:crossAx val="8915658"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1770,7 +1770,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="78246966"/>
+        <c:axId val="8915658"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1810,7 +1810,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38867580"/>
+        <c:crossAx val="588413"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2869,13 +2869,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Digite 0, 1, 2 ou 3." errorStyle="stop" errorTitle="Nível inválido" operator="between" prompt="0 não conhece · 1 com acompanhamento · 2 sozinho · 3 treina os outros" promptTitle="Nível" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D10:O19" type="whole">
+      <formula1>0</formula1>
+      <formula2>3</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D5" type="date">
       <formula1>36526</formula1>
       <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite 0, 1, 2 ou 3." errorStyle="stop" errorTitle="Nível inválido" operator="between" prompt="0 não conhece · 1 com acompanhamento · 2 sozinho · 3 treina os outros" promptTitle="Nível" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D10:O19" type="whole">
-      <formula1>0</formula1>
-      <formula2>3</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
@@ -5808,13 +5808,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Escolha uma função cadastrada na aba Funções." errorStyle="stop" errorTitle="Função inválida" operator="between" prompt="Escolha uma função da aba Funções." promptTitle="Função" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D10:D29" type="list">
+      <formula1>Funções!$C$10:$C$19</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Digite 0, 1, 2 ou 3." errorStyle="stop" errorTitle="Nível inválido" operator="between" prompt="0 não conhece · 1 com acompanhamento · 2 sozinho · 3 treina os outros" promptTitle="Nível" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="E10:P29" type="whole">
       <formula1>0</formula1>
       <formula2>3</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Escolha uma função cadastrada na aba Funções." errorStyle="stop" errorTitle="Função inválida" operator="between" prompt="Escolha uma função da aba Funções." promptTitle="Função" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D10:D29" type="list">
-      <formula1>Funções!$C$10:$C$19</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>

--- a/Competencias/Competencias-modelo.xlsx
+++ b/Competencias/Competencias-modelo.xlsx
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Checklist!$B$1:$E$24</definedName>
     <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 1 - Pizzaria'!$B$1:$O$50</definedName>
-    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 2 - Compras'!$B$1:$O$48</definedName>
+    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 2 - Compras'!$B$1:$O$50</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Funções!$B$1:$P$24</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instruções!$B$1:$C$43</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Matriz!$B$1:$T$53</definedName>
@@ -140,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="282">
   <si>
     <t xml:space="preserve">Matriz de competências e treinamento — Como usar esta planilha</t>
   </si>
@@ -562,390 +562,393 @@
     <t xml:space="preserve">Sim</t>
   </si>
   <si>
+    <t xml:space="preserve">Parcial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regula a temperatura; ainda não regula a chama do lastro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcial: reforçar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ações registradas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planejadas, no prazo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atrasadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizadas, a avaliar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eficazes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A reforçar ou refazer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registros de treinamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Um treinamento por linha, com a evidência de que aconteceu e de que o aprendizado foi avaliado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrutor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carga horária</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Participantes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprendizado avaliado?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do treinamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assunto e padrão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Em horas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Número de pessoas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lista de presença, prova, certificado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT-EXP-01: agrupamento por zona e conferência do pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sérgio, líder da expedição</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lista de presença e demonstração no posto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treinamentos registrados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horas de treinamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pessoas-hora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checklist da matriz de competências</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escolha o status de cada item na lista suspensa (coluna em amarelo-claro).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item de verificação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observações</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As funções que afetam a qualidade estão listadas, com as competências que cada uma exige.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A escala de níveis está escrita e foi entendida pelos líderes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada pessoa foi avaliada em cada competência da sua função, com evidência.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As lacunas estão identificadas: nível abaixo do requerido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada lacuna tem uma ação no plano, com responsável e prazo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada competência crítica tem pelo menos duas pessoas no nível 2 ou mais.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Os treinamentos realizados têm registro: data, tema, instrutor e presença.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O aprendizado é avaliado no fim de cada treinamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A eficácia é avaliada no posto de trabalho, depois de um prazo definido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A matriz é atualizada depois da avaliação da eficácia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quem entra na equipe passa pela integração antes de trabalhar sozinho.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As pessoas sabem responder às perguntas de conscientização: política, objetivos, contribuição e consequências.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Itens atendidos (Sim)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Itens parciais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Itens não atendidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Itens sem resposta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentual atendido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matriz de competências e treinamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exemplo preenchido, para consulta. Use as abas Funções, Matriz, Plano e Registros para a sua equipe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pizzaria (loja com salão e delivery)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gerente da loja, com os três líderes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A cada seis meses, e a cada admissão ou mudança de função.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Origem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Processo “Treinar a equipe” com 31% dos elementos definidos no mapa de 14/10/2026, e risco R6: só o pizzaiolo líder regula o forno.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Competências e nível requerido por função</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Competência →</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nome da competência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registrar o pedido pelo roteiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produzir no padrão das receitas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regular o forno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controlar a temperatura e as boas práticas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embalar e conferir o pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agrupar por zona e entregar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dirigir com segurança</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atender no salão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gerente da loja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atendente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pizzaiolo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Líder da expedição</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entregador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matriz · níveis em 12/02/2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sérgio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Igor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Célula com borda vermelha: lacuna, nível abaixo do requerido pela função.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acompanhamento das receitas com maior desperdício, com conferência do pizzaiolo líder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treinamento em boas práticas e controle de temperatura, com prova.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conferência do pedido com o líder da expedição, nas noites de sexta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atendimento no salão, depois do padrão de atendimento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treinamento na IT-EXP-01, com o líder da expedição.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integração: boas práticas de manipulação.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Competências com uma só pessoa no nível 2, ou nenhuma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Competências sem ninguém no nível 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ações no plano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ações eficazes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ações atrasadas, ou a refazer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indústria de embalagens plásticas · Suprimentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gerente de Suprimentos, com o Coordenador da Qualidade e o RH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A cada seis meses, com a avaliação de desempenho.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisão 6 do PR-SUP-01, admissão de um comprador em janeiro e decisão da análise crítica de 18/02/2027: formar mais quatro auditores internos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplicar o PR-SUP-01 rev. 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Especificar itens e usar o cadastro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cotar e negociar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologar e avaliar fornecedores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operar o sistema de compras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receber e conferir materiais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requisitos da ISO 9001 para aquisição</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auditar processos internamente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gerente de Suprimentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Líder do Recebimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matriz · níveis em 12/03/2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antônio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felipe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jorge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integração: leitura do PR-SUP-01 rev. 6 e prova de 10 questões.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Eficaz</t>
   </si>
   <si>
-    <t xml:space="preserve">Regulou o forno sozinho em 8 turnos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ações registradas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planejadas, no prazo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atrasadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizadas, a avaliar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eficazes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A reforçar ou refazer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registros de treinamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Um treinamento por linha, com a evidência de que aconteceu e de que o aprendizado foi avaliado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instrutor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carga horária</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Participantes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aprendizado avaliado?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidência</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Do treinamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assunto e padrão</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Em horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de pessoas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lista de presença, prova, certificado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT-EXP-01: agrupamento por zona e conferência do pedido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sérgio, líder da expedição</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lista de presença e demonstração no posto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treinamentos registrados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas de treinamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pessoas-hora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checklist da matriz de competências</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escolha o status de cada item na lista suspensa (coluna em amarelo-claro).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item de verificação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observações</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As funções que afetam a qualidade estão listadas, com as competências que cada uma exige.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A escala de níveis está escrita e foi entendida pelos líderes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cada pessoa foi avaliada em cada competência da sua função, com evidência.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As lacunas estão identificadas: nível abaixo do requerido.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cada lacuna tem uma ação no plano, com responsável e prazo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cada competência crítica tem pelo menos duas pessoas no nível 2 ou mais.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Os treinamentos realizados têm registro: data, tema, instrutor e presença.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O aprendizado é avaliado no fim de cada treinamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A eficácia é avaliada no posto de trabalho, depois de um prazo definido.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A matriz é atualizada depois da avaliação da eficácia.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quem entra na equipe passa pela integração antes de trabalhar sozinho.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As pessoas sabem responder às perguntas de conscientização: política, objetivos, contribuição e consequências.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Itens atendidos (Sim)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Itens parciais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Itens não atendidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Itens sem resposta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percentual atendido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matriz de competências e treinamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exemplo preenchido, para consulta. Use as abas Funções, Matriz, Plano e Registros para a sua equipe.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pizzaria (loja com salão e delivery)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gerente da loja, com os três líderes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revisão</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A cada seis meses, e a cada admissão ou mudança de função.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Origem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Processo “Treinar a equipe” com 31% dos elementos definidos no mapa de 14/10/2026, e risco R6: só o pizzaiolo líder regula o forno.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Competências e nível requerido por função</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Competência →</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome da competência</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registrar o pedido pelo roteiro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produzir no padrão das receitas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regular o forno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controlar a temperatura e as boas práticas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embalar e conferir o pedido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agrupar por zona e entregar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dirigir com segurança</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atender no salão</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gerente da loja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atendente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pizzaiolo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Líder da expedição</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entregador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matriz · níveis em 12/02/2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diego</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sérgio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Igor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Célula com borda vermelha: lacuna, nível abaixo do requerido pela função.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acompanhamento das receitas com maior desperdício, com conferência do pizzaiolo líder.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treinamento em boas práticas e controle de temperatura, com prova.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conferência do pedido com o líder da expedição, nas noites de sexta.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atendimento no salão, depois do padrão de atendimento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treinamento na IT-EXP-01, com o líder da expedição.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integração: boas práticas de manipulação.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Competências com uma só pessoa no nível 2, ou nenhuma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Competências sem ninguém no nível 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ações no plano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ações eficazes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ações atrasadas, ou a refazer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indústria de embalagens plásticas · Suprimentos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gerente de Suprimentos, com o Coordenador da Qualidade e o RH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A cada seis meses, com a avaliação de desempenho.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revisão 6 do PR-SUP-01, admissão de um comprador em janeiro e decisão da análise crítica de 18/02/2027: formar mais quatro auditores internos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplicar o PR-SUP-01 rev. 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Especificar itens e usar o cadastro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cotar e negociar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homologar e avaliar fornecedores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operar o sistema de compras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receber e conferir materiais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requisitos da ISO 9001 para aquisição</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auditar processos internamente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gerente de Suprimentos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comprador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Líder do Recebimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matriz · níveis em 12/03/2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antônio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Felipe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camila</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jorge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integração: leitura do PR-SUP-01 rev. 6 e prova de 10 questões.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Treinamento no sistema de compras, com 20 requisições acompanhadas.</t>
   </si>
   <si>
@@ -961,6 +964,15 @@
     <t xml:space="preserve">Homologação de fornecedores: participar de duas homologações.</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebimento: conferir os materiais com o líder do Recebimento, duas semanas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curso interno: requisitos da ISO 9001 para aquisição, 4 horas, na próxima turma.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordenador da Qualidade</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reciclagem no PR-SUP-01 rev. 6, com foco no cadastro do item antes da compra.</t>
   </si>
   <si>
@@ -971,9 +983,6 @@
   </si>
   <si>
     <t xml:space="preserve">Curso interno: requisitos da ISO 9001 para aquisição, 4 horas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coordenador da Qualidade</t>
   </si>
   <si>
     <t xml:space="preserve">Formação de auditor interno: curso de 16 horas e duas auditorias acompanhadas.</t>
@@ -1726,11 +1735,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="588413"/>
-        <c:axId val="8915658"/>
+        <c:axId val="87690838"/>
+        <c:axId val="19270164"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="588413"/>
+        <c:axId val="87690838"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1762,7 +1771,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8915658"/>
+        <c:crossAx val="19270164"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1770,7 +1779,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="8915658"/>
+        <c:axId val="19270164"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1810,7 +1819,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="588413"/>
+        <c:crossAx val="87690838"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -5991,7 +6000,7 @@
         <v>141</v>
       </c>
       <c r="M6" s="24" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6487,7 +6496,7 @@
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C34" s="19"/>
       <c r="D34" s="19"/>
@@ -6499,7 +6508,7 @@
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C35" s="19"/>
       <c r="D35" s="19"/>
@@ -6511,7 +6520,7 @@
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C36" s="19"/>
       <c r="D36" s="19"/>
@@ -6523,7 +6532,7 @@
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C37" s="19"/>
       <c r="D37" s="19"/>
@@ -6535,7 +6544,7 @@
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C38" s="19"/>
       <c r="D38" s="19"/>
@@ -6547,7 +6556,7 @@
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C39" s="19"/>
       <c r="D39" s="19"/>
@@ -6675,7 +6684,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -6688,7 +6697,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -6704,25 +6713,25 @@
         <v>85</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J4" s="16" t="s">
         <v>99</v>
@@ -6731,25 +6740,25 @@
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="24"/>
       <c r="C5" s="24" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E5" s="24" t="s">
         <v>128</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H5" s="24" t="s">
         <v>131</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J5" s="24" t="s">
         <v>104</v>
@@ -6763,10 +6772,10 @@
         <v>46323</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F6" s="24" t="n">
         <v>2</v>
@@ -6778,10 +6787,10 @@
         <v>139</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7199,7 +7208,7 @@
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C34" s="19"/>
       <c r="D34" s="19"/>
@@ -7211,7 +7220,7 @@
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C35" s="19"/>
       <c r="D35" s="19"/>
@@ -7223,7 +7232,7 @@
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C36" s="19"/>
       <c r="D36" s="19"/>
@@ -7322,7 +7331,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -7330,7 +7339,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -7341,13 +7350,13 @@
         <v>85</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7355,7 +7364,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="5"/>
@@ -7365,7 +7374,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="5"/>
@@ -7375,7 +7384,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="5"/>
@@ -7385,7 +7394,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="5"/>
@@ -7395,7 +7404,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="5"/>
@@ -7405,7 +7414,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="5"/>
@@ -7415,7 +7424,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="5"/>
@@ -7425,7 +7434,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="5"/>
@@ -7435,7 +7444,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="5"/>
@@ -7445,7 +7454,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="5"/>
@@ -7455,7 +7464,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="5"/>
@@ -7465,7 +7474,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D16" s="15"/>
       <c r="E16" s="5"/>
@@ -7480,7 +7489,7 @@
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C19" s="19"/>
       <c r="D19" s="29" t="n">
@@ -7490,7 +7499,7 @@
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="19" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C20" s="19"/>
       <c r="D20" s="29" t="n">
@@ -7500,7 +7509,7 @@
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C21" s="19"/>
       <c r="D21" s="29" t="n">
@@ -7510,7 +7519,7 @@
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C22" s="19"/>
       <c r="D22" s="29" t="n">
@@ -7520,7 +7529,7 @@
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="30" t="n">
@@ -7599,7 +7608,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -7617,7 +7626,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -7638,7 +7647,7 @@
         <v>69</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D4" s="37"/>
       <c r="E4" s="37"/>
@@ -7675,10 +7684,10 @@
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D6" s="37"/>
       <c r="E6" s="37"/>
@@ -7695,10 +7704,10 @@
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D7" s="37"/>
       <c r="E7" s="37"/>
@@ -7715,10 +7724,10 @@
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D8" s="37"/>
       <c r="E8" s="37"/>
@@ -7735,7 +7744,7 @@
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C10" s="39"/>
       <c r="D10" s="39"/>
@@ -7756,7 +7765,7 @@
         <v>86</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D11" s="29" t="s">
         <v>72</v>
@@ -7786,36 +7795,36 @@
     <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="6"/>
       <c r="C12" s="24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H12" s="25" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J12" s="25" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K12" s="25" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="40" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C13" s="40"/>
       <c r="D13" s="41" t="n">
@@ -7845,7 +7854,7 @@
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="40" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C14" s="40"/>
       <c r="D14" s="41" t="n">
@@ -7875,7 +7884,7 @@
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="40" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C15" s="40"/>
       <c r="D15" s="41" t="n">
@@ -7905,7 +7914,7 @@
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="40" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C16" s="40"/>
       <c r="D16" s="41" t="n">
@@ -7935,7 +7944,7 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="40" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C17" s="40"/>
       <c r="D17" s="41" t="n">
@@ -7965,7 +7974,7 @@
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="42" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C19" s="42"/>
       <c r="D19" s="42"/>
@@ -8025,10 +8034,10 @@
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="40" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D21" s="41" t="n">
         <v>3</v>
@@ -8070,10 +8079,10 @@
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="40" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D22" s="41" t="n">
         <v>3</v>
@@ -8115,10 +8124,10 @@
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="40" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D23" s="41" t="n">
         <v>2</v>
@@ -8163,7 +8172,7 @@
         <v>138</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D24" s="41" t="n">
         <v>0</v>
@@ -8208,7 +8217,7 @@
         <v>136</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D25" s="41" t="n">
         <v>0</v>
@@ -8216,8 +8225,8 @@
       <c r="E25" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="F25" s="41" t="n">
-        <v>2</v>
+      <c r="F25" s="43" t="n">
+        <v>1</v>
       </c>
       <c r="G25" s="43" t="n">
         <v>2</v>
@@ -8236,11 +8245,11 @@
       </c>
       <c r="L25" s="17" t="n">
         <f aca="false">SUMPRODUCT((D15:K15&gt;D25:K25)*1)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M25" s="26" t="n">
         <f aca="false">1-L25/COUNTIF(D15:K15,"&gt;0")</f>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="N25" s="21" t="str">
         <f aca="false">IF(L25=0,"Sem lacunas","Com lacunas")</f>
@@ -8250,10 +8259,10 @@
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="40" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D26" s="41" t="n">
         <v>1</v>
@@ -8295,10 +8304,10 @@
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="40" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D27" s="41" t="n">
         <v>0</v>
@@ -8340,10 +8349,10 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="40" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D28" s="41" t="n">
         <v>0</v>
@@ -8398,7 +8407,7 @@
       </c>
       <c r="F29" s="29" t="n">
         <f aca="false">COUNTIF(F21:F28,"&gt;=2")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="29" t="n">
         <f aca="false">COUNTIF(G21:G28,"&gt;=2")</f>
@@ -8469,7 +8478,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="44" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C31" s="44"/>
       <c r="D31" s="44"/>
@@ -8508,7 +8517,7 @@
         <v>95</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D34" s="20" t="s">
         <v>117</v>
@@ -8525,7 +8534,7 @@
       </c>
       <c r="K34" s="20"/>
       <c r="L34" s="29" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M34" s="29" t="s">
         <v>121</v>
@@ -8569,7 +8578,7 @@
       </c>
       <c r="O35" s="21" t="str">
         <f aca="false">IF(D35="","",IF(L35="",IF(J35="","Falta o prazo",IF(J35&lt;$C$5,"Atrasada","Planejada")),IF(M35="","Falta a avaliação de aprendizado",IF(M35="Não","Não eficaz: refazer",IF(N35="",IF(L35+60&lt;=$C$5,"Avaliar a eficácia","Em acompanhamento"),IF(N35="Eficaz","Eficaz",IF(N35="Parcial","Parcial: reforçar","Não eficaz: refazer")))))))</f>
-        <v>Eficaz</v>
+        <v>Parcial: reforçar</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8580,7 +8589,7 @@
         <v>73</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
@@ -8613,13 +8622,13 @@
         <v>75</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
       <c r="H37" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I37" s="7"/>
       <c r="J37" s="46" t="n">
@@ -8640,19 +8649,19 @@
     </row>
     <row r="38" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="40" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C38" s="41" t="s">
         <v>76</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
       <c r="H38" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I38" s="7"/>
       <c r="J38" s="46" t="n">
@@ -8669,19 +8678,19 @@
     </row>
     <row r="39" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="40" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C39" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
       <c r="H39" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I39" s="7"/>
       <c r="J39" s="46" t="n">
@@ -8698,19 +8707,19 @@
     </row>
     <row r="40" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="40" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C40" s="41" t="s">
         <v>77</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
       <c r="H40" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I40" s="7"/>
       <c r="J40" s="46" t="n">
@@ -8724,7 +8733,7 @@
         <v>139</v>
       </c>
       <c r="N40" s="41" t="s">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="O40" s="21" t="str">
         <f aca="false">IF(D40="","",IF(L40="",IF(J40="","Falta o prazo",IF(J40&lt;$C$5,"Atrasada","Planejada")),IF(M40="","Falta a avaliação de aprendizado",IF(M40="Não","Não eficaz: refazer",IF(N40="",IF(L40+60&lt;=$C$5,"Avaliar a eficácia","Em acompanhamento"),IF(N40="Eficaz","Eficaz",IF(N40="Parcial","Parcial: reforçar","Não eficaz: refazer")))))))</f>
@@ -8733,7 +8742,7 @@
     </row>
     <row r="41" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="40" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C41" s="41" t="s">
         <v>75</v>
@@ -8745,7 +8754,7 @@
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
       <c r="H41" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I41" s="7"/>
       <c r="J41" s="46" t="n">
@@ -8799,7 +8808,7 @@
       <c r="E45" s="19"/>
       <c r="F45" s="29" t="n">
         <f aca="false">SUM(L21:L28)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8811,7 +8820,7 @@
       <c r="E46" s="19"/>
       <c r="F46" s="29" t="n">
         <f aca="false">COUNTIF(D29:K29,"&lt;2")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8847,7 +8856,7 @@
       <c r="E49" s="19"/>
       <c r="F49" s="29" t="n">
         <f aca="false">COUNTIF(O35:O41,"Eficaz")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9008,7 +9017,7 @@
     <tabColor rgb="FF5B6B76"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:O48"/>
+  <dimension ref="B1:O50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -9024,7 +9033,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -9042,7 +9051,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -9100,7 +9109,7 @@
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C6" s="37" t="s">
         <v>238</v>
@@ -9120,7 +9129,7 @@
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C7" s="37" t="s">
         <v>239</v>
@@ -9140,7 +9149,7 @@
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C8" s="37" t="s">
         <v>240</v>
@@ -9160,7 +9169,7 @@
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C10" s="39"/>
       <c r="D10" s="39"/>
@@ -9181,7 +9190,7 @@
         <v>86</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D11" s="29" t="s">
         <v>241</v>
@@ -9211,7 +9220,7 @@
     <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="6"/>
       <c r="C12" s="24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D12" s="25" t="s">
         <v>249</v>
@@ -9744,7 +9753,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="44" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C27" s="44"/>
       <c r="D27" s="44"/>
@@ -9783,7 +9792,7 @@
         <v>95</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D30" s="20" t="s">
         <v>117</v>
@@ -9800,7 +9809,7 @@
       </c>
       <c r="K30" s="20"/>
       <c r="L30" s="29" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M30" s="29" t="s">
         <v>121</v>
@@ -9840,7 +9849,7 @@
         <v>139</v>
       </c>
       <c r="N31" s="41" t="s">
-        <v>140</v>
+        <v>268</v>
       </c>
       <c r="O31" s="21" t="str">
         <f aca="false">IF(D31="","",IF(L31="",IF(J31="","Falta o prazo",IF(J31&lt;$C$5,"Atrasada","Planejada")),IF(M31="","Falta a avaliação de aprendizado",IF(M31="Não","Não eficaz: refazer",IF(N31="",IF(L31+60&lt;=$C$5,"Avaliar a eficácia","Em acompanhamento"),IF(N31="Eficaz","Eficaz",IF(N31="Parcial","Parcial: reforçar","Não eficaz: refazer")))))))</f>
@@ -9855,7 +9864,7 @@
         <v>245</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
@@ -9888,13 +9897,13 @@
         <v>242</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="H33" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I33" s="7"/>
       <c r="J33" s="46" t="n">
@@ -9917,7 +9926,7 @@
         <v>243</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
@@ -9946,7 +9955,7 @@
         <v>244</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
@@ -9969,45 +9978,39 @@
     </row>
     <row r="36" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="40" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C36" s="41" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
       <c r="H36" s="7" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="46" t="n">
-        <v>46339</v>
+        <v>46493</v>
       </c>
       <c r="K36" s="46"/>
-      <c r="L36" s="46" t="n">
-        <v>46336</v>
-      </c>
-      <c r="M36" s="41" t="s">
-        <v>139</v>
-      </c>
-      <c r="N36" s="41" t="s">
-        <v>274</v>
-      </c>
+      <c r="L36" s="46"/>
+      <c r="M36" s="41"/>
+      <c r="N36" s="41"/>
       <c r="O36" s="21" t="str">
         <f aca="false">IF(D36="","",IF(L36="",IF(J36="","Falta o prazo",IF(J36&lt;$C$5,"Atrasada","Planejada")),IF(M36="","Falta a avaliação de aprendizado",IF(M36="Não","Não eficaz: refazer",IF(N36="",IF(L36+60&lt;=$C$5,"Avaliar a eficácia","Em acompanhamento"),IF(N36="Eficaz","Eficaz",IF(N36="Parcial","Parcial: reforçar","Não eficaz: refazer")))))))</f>
-        <v>Não eficaz: refazer</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>Planejada</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="40" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C37" s="41" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>275</v>
@@ -10016,11 +10019,11 @@
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
       <c r="H37" s="7" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="I37" s="7"/>
       <c r="J37" s="46" t="n">
-        <v>46568</v>
+        <v>46563</v>
       </c>
       <c r="K37" s="46"/>
       <c r="L37" s="46"/>
@@ -10033,56 +10036,58 @@
     </row>
     <row r="38" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="40" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
       <c r="H38" s="7" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="I38" s="7"/>
       <c r="J38" s="46" t="n">
-        <v>46444</v>
+        <v>46339</v>
       </c>
       <c r="K38" s="46"/>
       <c r="L38" s="46" t="n">
-        <v>46442</v>
+        <v>46336</v>
       </c>
       <c r="M38" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="N38" s="41"/>
+      <c r="N38" s="41" t="s">
+        <v>278</v>
+      </c>
       <c r="O38" s="21" t="str">
         <f aca="false">IF(D38="","",IF(L38="",IF(J38="","Falta o prazo",IF(J38&lt;$C$5,"Atrasada","Planejada")),IF(M38="","Falta a avaliação de aprendizado",IF(M38="Não","Não eficaz: refazer",IF(N38="",IF(L38+60&lt;=$C$5,"Avaliar a eficácia","Em acompanhamento"),IF(N38="Eficaz","Eficaz",IF(N38="Parcial","Parcial: reforçar","Não eficaz: refazer")))))))</f>
-        <v>Em acompanhamento</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>Não eficaz: refazer</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="40" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
       <c r="H39" s="7" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="I39" s="7"/>
       <c r="J39" s="46" t="n">
-        <v>46535</v>
+        <v>46568</v>
       </c>
       <c r="K39" s="46"/>
       <c r="L39" s="46"/>
@@ -10093,110 +10098,172 @@
         <v>Planejada</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="18" t="s">
+    <row r="40" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="40" t="s">
+        <v>264</v>
+      </c>
+      <c r="C40" s="41" t="s">
+        <v>247</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="I40" s="7"/>
+      <c r="J40" s="46" t="n">
+        <v>46444</v>
+      </c>
+      <c r="K40" s="46"/>
+      <c r="L40" s="46" t="n">
+        <v>46442</v>
+      </c>
+      <c r="M40" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="N40" s="41"/>
+      <c r="O40" s="21" t="str">
+        <f aca="false">IF(D40="","",IF(L40="",IF(J40="","Falta o prazo",IF(J40&lt;$C$5,"Atrasada","Planejada")),IF(M40="","Falta a avaliação de aprendizado",IF(M40="Não","Não eficaz: refazer",IF(N40="",IF(L40+60&lt;=$C$5,"Avaliar a eficácia","Em acompanhamento"),IF(N40="Eficaz","Eficaz",IF(N40="Parcial","Parcial: reforçar","Não eficaz: refazer")))))))</f>
+        <v>Em acompanhamento</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="40" t="s">
+        <v>261</v>
+      </c>
+      <c r="C41" s="41" t="s">
+        <v>248</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="I41" s="7"/>
+      <c r="J41" s="46" t="n">
+        <v>46535</v>
+      </c>
+      <c r="K41" s="46"/>
+      <c r="L41" s="46"/>
+      <c r="M41" s="41"/>
+      <c r="N41" s="41"/>
+      <c r="O41" s="21" t="str">
+        <f aca="false">IF(D41="","",IF(L41="",IF(J41="","Falta o prazo",IF(J41&lt;$C$5,"Atrasada","Planejada")),IF(M41="","Falta a avaliação de aprendizado",IF(M41="Não","Não eficaz: refazer",IF(N41="",IF(L41+60&lt;=$C$5,"Avaliar a eficácia","Em acompanhamento"),IF(N41="Eficaz","Eficaz",IF(N41="Parcial","Parcial: reforçar","Não eficaz: refazer")))))))</f>
+        <v>Planejada</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="18"/>
-      <c r="K41" s="18"/>
-      <c r="L41" s="18"/>
-      <c r="M41" s="18"/>
-      <c r="N41" s="18"/>
-      <c r="O41" s="18"/>
-    </row>
-    <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="29" t="n">
-        <f aca="false">COUNTA(B19:B24)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="29" t="n">
-        <f aca="false">SUM(L19:L24)</f>
-        <v>11</v>
-      </c>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="18"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="18"/>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="19" t="s">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="C44" s="19"/>
       <c r="D44" s="19"/>
       <c r="E44" s="19"/>
       <c r="F44" s="29" t="n">
-        <f aca="false">COUNTIF(D25:K25,"&lt;2")</f>
-        <v>2</v>
+        <f aca="false">COUNTA(B19:B24)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="19" t="s">
-        <v>233</v>
+        <v>97</v>
       </c>
       <c r="C45" s="19"/>
       <c r="D45" s="19"/>
       <c r="E45" s="19"/>
       <c r="F45" s="29" t="n">
-        <f aca="false">COUNTIF(D26:K26,0)</f>
-        <v>2</v>
+        <f aca="false">SUM(L19:L24)</f>
+        <v>11</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="19" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C46" s="19"/>
       <c r="D46" s="19"/>
       <c r="E46" s="19"/>
       <c r="F46" s="29" t="n">
-        <f aca="false">COUNTA(B31:B39)</f>
-        <v>9</v>
+        <f aca="false">COUNTIF(D25:K25,"&lt;2")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="19" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C47" s="19"/>
       <c r="D47" s="19"/>
       <c r="E47" s="19"/>
       <c r="F47" s="29" t="n">
-        <f aca="false">COUNTIF(O31:O39,"Eficaz")</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(D26:K26,0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="19" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C48" s="19"/>
       <c r="D48" s="19"/>
       <c r="E48" s="19"/>
       <c r="F48" s="29" t="n">
-        <f aca="false">COUNTIF(O31:O39,"Atrasada")+COUNTIF(O31:O39,"Não eficaz: refazer")</f>
+        <f aca="false">COUNTA(B31:B41)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="29" t="n">
+        <f aca="false">COUNTIF(O31:O41,"Eficaz")</f>
         <v>1</v>
       </c>
     </row>
+    <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B50" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="29" t="n">
+        <f aca="false">COUNTIF(O31:O41,"Atrasada")+COUNTIF(O31:O41,"Não eficaz: refazer")</f>
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="61">
+  <mergeCells count="67">
     <mergeCell ref="B1:O1"/>
     <mergeCell ref="B2:O2"/>
     <mergeCell ref="C4:O4"/>
@@ -10250,14 +10317,20 @@
     <mergeCell ref="D39:G39"/>
     <mergeCell ref="H39:I39"/>
     <mergeCell ref="J39:K39"/>
-    <mergeCell ref="B41:O41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="B43:O43"/>
     <mergeCell ref="B44:E44"/>
     <mergeCell ref="B45:E45"/>
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="B47:E47"/>
     <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
   </mergeCells>
   <conditionalFormatting sqref="D13:K15">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -10295,7 +10368,7 @@
       <formula>N19="Com lacunas"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O31:O39">
+  <conditionalFormatting sqref="O31:O41">
     <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>O31="Eficaz"</formula>
     </cfRule>
